--- a/data/trans_dic/ProbViv_temp-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_temp-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas de temperatura en la vivienda</t>
+          <t>Hogares con problemas de temperatura en la vivienda (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,59; 50,49</t>
+          <t>19,43; 51,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,8; 31,97</t>
+          <t>13,24; 32,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,05; 36,87</t>
+          <t>18,88; 36,27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,56; 68,49</t>
+          <t>12,61; 68,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,32; 15,51</t>
+          <t>5,7; 16,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,8; 47,34</t>
+          <t>10,98; 53,31</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,85; 51,43</t>
+          <t>31,68; 50,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,74; 45,96</t>
+          <t>27,26; 46,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31,39; 44,71</t>
+          <t>31,42; 45,56</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,89; 38,57</t>
+          <t>18,6; 37,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,01; 26,33</t>
+          <t>8,7; 27,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,5; 27,79</t>
+          <t>14,66; 28,76</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,58; 40,21</t>
+          <t>17,25; 39,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,99; 43,2</t>
+          <t>18,95; 42,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,13; 36,78</t>
+          <t>21,62; 37,58</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,78; 31,64</t>
+          <t>12,68; 29,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,43; 30,72</t>
+          <t>13,68; 29,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15,63; 26,95</t>
+          <t>15,37; 27,9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30,76; 46,79</t>
+          <t>31,35; 47,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>31,3; 47,11</t>
+          <t>30,73; 47,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>32,95; 43,97</t>
+          <t>33,3; 44,87</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77,11; 89,15</t>
+          <t>78,59; 89,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>81,42; 91,09</t>
+          <t>80,79; 90,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>81,95; 89,2</t>
+          <t>81,92; 89,04</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39,19; 51,12</t>
+          <t>38,79; 51,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>34,01; 40,85</t>
+          <t>34,07; 40,83</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>37,46; 43,91</t>
+          <t>37,37; 44,14</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con problemas de temperatura en la vivienda (tasa de respuesta: 99,97%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22819</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>17186</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>40005</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>14241; 37482</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>10506; 25475</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>28820; 55370</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>42526</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>12577</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>55103</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>16100; 87772</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>7268; 20479</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>28030; 136065</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>24015</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>24190</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>48205</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18459; 29507</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>18310; 30925</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>39410; 57145</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>19147</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>12503</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>31650</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>12864; 26186</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>6796; 21363</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>21593; 42357</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>9465</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>11992</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>21457</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5955; 13501</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>7718; 17232</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>16262; 28271</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>9673</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>11702</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>21375</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>5853; 13818</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>7685; 16731</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>15733; 28557</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>47854</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>60662</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>108517</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>39038; 58526</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>47660; 73900</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>93104; 125457</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>111063</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>135977</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>247040</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>103443; 117869</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>126677; 142460</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>236274; 256804</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>286563</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>286789</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>573352</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>257984; 342875</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>259269; 310694</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>532894; 629449</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/ProbViv_temp-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_temp-Provincia-trans_dic.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,43; 51,15</t>
+          <t>20,37; 51,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,24; 32,1</t>
+          <t>14,11; 34,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,88; 36,27</t>
+          <t>18,23; 36,62</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,61; 68,76</t>
+          <t>13,36; 70,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 16,05</t>
+          <t>5,75; 16,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,98; 53,31</t>
+          <t>10,74; 47,38</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,68; 50,64</t>
+          <t>30,85; 50,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,26; 46,05</t>
+          <t>27,14; 46,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31,42; 45,56</t>
+          <t>30,86; 44,99</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,6; 37,87</t>
+          <t>18,74; 37,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,7; 27,34</t>
+          <t>8,43; 26,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,66; 28,76</t>
+          <t>14,88; 28,15</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,25; 39,12</t>
+          <t>17,55; 39,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,95; 42,32</t>
+          <t>19,41; 42,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,62; 37,58</t>
+          <t>21,68; 36,77</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,68; 29,93</t>
+          <t>12,88; 31,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,68; 29,78</t>
+          <t>13,3; 29,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15,37; 27,9</t>
+          <t>14,78; 27,63</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31,35; 47,01</t>
+          <t>31,65; 47,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>30,73; 47,66</t>
+          <t>30,91; 47,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,3; 44,87</t>
+          <t>33,36; 44,59</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78,59; 89,55</t>
+          <t>78,06; 89,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>80,79; 90,86</t>
+          <t>81,56; 90,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>81,92; 89,04</t>
+          <t>81,75; 88,89</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38,79; 51,55</t>
+          <t>38,49; 50,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>34,07; 40,83</t>
+          <t>34,25; 41,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>37,37; 44,14</t>
+          <t>37,58; 44,39</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14241; 37482</t>
+          <t>14928; 37371</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10506; 25475</t>
+          <t>11202; 26987</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28820; 55370</t>
+          <t>27824; 55893</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16100; 87772</t>
+          <t>17055; 89803</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7268; 20479</t>
+          <t>7343; 20561</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>28030; 136065</t>
+          <t>27411; 120947</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18459; 29507</t>
+          <t>17974; 29698</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18310; 30925</t>
+          <t>18229; 31017</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>39410; 57145</t>
+          <t>38705; 56433</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12864; 26186</t>
+          <t>12955; 26134</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6796; 21363</t>
+          <t>6587; 20424</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21593; 42357</t>
+          <t>21912; 41462</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5955; 13501</t>
+          <t>6057; 13702</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7718; 17232</t>
+          <t>7905; 17223</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16262; 28271</t>
+          <t>16308; 27659</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5853; 13818</t>
+          <t>5948; 14720</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7685; 16731</t>
+          <t>7474; 16665</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15733; 28557</t>
+          <t>15126; 28283</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39038; 58526</t>
+          <t>39402; 58928</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>47660; 73900</t>
+          <t>47934; 73576</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>93104; 125457</t>
+          <t>93272; 124663</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>103443; 117869</t>
+          <t>102745; 117206</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>126677; 142460</t>
+          <t>127876; 142416</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>236274; 256804</t>
+          <t>235775; 256377</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>257984; 342875</t>
+          <t>256029; 338376</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>259269; 310694</t>
+          <t>260623; 312103</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>532894; 629449</t>
+          <t>535925; 633137</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProbViv_temp-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_temp-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,37; 51,0</t>
+          <t>10,22; 25,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,11; 34,0</t>
+          <t>14,33; 31,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,23; 36,62</t>
+          <t>14,64; 25,53</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,36; 70,35</t>
+          <t>5,27; 15,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,75; 16,11</t>
+          <t>9,99; 25,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,74; 47,38</t>
+          <t>8,9; 17,86</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,75%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,85; 50,97</t>
+          <t>26,38; 45,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,14; 46,18</t>
+          <t>31,2; 51,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30,86; 44,99</t>
+          <t>31,71; 45,1</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,74; 37,8</t>
+          <t>8,73; 27,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,43; 26,14</t>
+          <t>17,73; 37,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,88; 28,15</t>
+          <t>13,91; 27,67</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,55; 39,7</t>
+          <t>17,44; 39,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,41; 42,3</t>
+          <t>17,41; 40,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,68; 36,77</t>
+          <t>20,48; 34,86</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,88; 31,88</t>
+          <t>13,91; 31,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,3; 29,66</t>
+          <t>12,81; 31,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,78; 27,63</t>
+          <t>15,71; 27,21</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31,65; 47,33</t>
+          <t>31,76; 46,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>30,91; 47,45</t>
+          <t>30,73; 45,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,36; 44,59</t>
+          <t>33,07; 43,98</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,53%</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78,06; 89,05</t>
+          <t>81,49; 91,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>81,56; 90,83</t>
+          <t>76,27; 89,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>81,75; 88,89</t>
+          <t>81,78; 89,15</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38,49; 50,87</t>
+          <t>34,75; 41,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>34,25; 41,01</t>
+          <t>37,27; 43,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>37,58; 44,39</t>
+          <t>37,14; 42,0</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2088,27 +2088,27 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22819</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17186</t>
+          <t>12628</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40005</t>
+          <t>23399</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14928; 37371</t>
+          <t>6556; 16650</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11202; 26987</t>
+          <t>8096; 17746</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27824; 55893</t>
+          <t>17656; 30797</t>
         </is>
       </c>
     </row>
@@ -2296,27 +2296,27 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42526</t>
+          <t>11432</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12577</t>
+          <t>16044</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55103</t>
+          <t>27476</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17055; 89803</t>
+          <t>6107; 18195</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7343; 20561</t>
+          <t>10126; 26211</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>27411; 120947</t>
+          <t>19325; 38791</t>
         </is>
       </c>
     </row>
@@ -2504,27 +2504,27 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24015</t>
+          <t>21502</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24190</t>
+          <t>23428</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48205</t>
+          <t>44931</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17974; 29698</t>
+          <t>15661; 27290</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18229; 31017</t>
+          <t>17645; 29241</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38705; 56433</t>
+          <t>36768; 52286</t>
         </is>
       </c>
     </row>
@@ -2712,27 +2712,27 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19147</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>18518</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31650</t>
+          <t>30022</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12955; 26134</t>
+          <t>6300; 19879</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6587; 20424</t>
+          <t>12373; 26279</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21912; 41462</t>
+          <t>19747; 39267</t>
         </is>
       </c>
     </row>
@@ -2920,27 +2920,27 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9465</t>
+          <t>10710</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11992</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21457</t>
+          <t>20675</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6057; 13702</t>
+          <t>6901; 15640</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7905; 17223</t>
+          <t>6199; 14314</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16308; 27659</t>
+          <t>15395; 26214</t>
         </is>
       </c>
     </row>
@@ -3128,27 +3128,27 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9673</t>
+          <t>10420</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>11702</t>
+          <t>9694</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>21375</t>
+          <t>20114</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5948; 14720</t>
+          <t>6808; 15225</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7474; 16665</t>
+          <t>5862; 14407</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15126; 28283</t>
+          <t>14874; 25772</t>
         </is>
       </c>
     </row>
@@ -3336,27 +3336,27 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>66</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47854</t>
+          <t>55321</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>60662</t>
+          <t>46830</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>108517</t>
+          <t>102150</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39402; 58928</t>
+          <t>44599; 65438</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>47934; 73576</t>
+          <t>37649; 56324</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>93272; 124663</t>
+          <t>86944; 115643</t>
         </is>
       </c>
     </row>
@@ -3544,27 +3544,27 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>163</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>111063</t>
+          <t>138344</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>135977</t>
+          <t>118179</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>247040</t>
+          <t>256523</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>102745; 117206</t>
+          <t>129906; 145559</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>127876; 142416</t>
+          <t>107159; 125268</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>235775; 256377</t>
+          <t>245262; 267375</t>
         </is>
       </c>
     </row>
@@ -3752,27 +3752,27 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>368</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>286563</t>
+          <t>270003</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>286789</t>
+          <t>255288</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>573352</t>
+          <t>525290</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>256029; 338376</t>
+          <t>243222; 292631</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>260623; 312103</t>
+          <t>234289; 274834</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>535925; 633137</t>
+          <t>493395; 557944</t>
         </is>
       </c>
     </row>
